--- a/data/Неделя_14.09-20.09_2026.xlsx
+++ b/data/Неделя_14.09-20.09_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFE0573-5898-40D0-863B-C3BCB918C412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF902DD-8B3E-43A4-9D19-F27E5216A449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="84">
   <si>
     <t>№ п/п</t>
   </si>
@@ -793,21 +793,11 @@
       <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
       <c r="R2" s="5" t="s">
         <v>81</v>
       </c>
@@ -849,21 +839,11 @@
       <c r="L3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
       <c r="R3" s="5" t="s">
         <v>81</v>
       </c>
@@ -905,21 +885,11 @@
       <c r="L4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
       <c r="R4" s="5" t="s">
         <v>81</v>
       </c>
@@ -961,21 +931,11 @@
       <c r="L5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
       <c r="R5" s="5" t="s">
         <v>81</v>
       </c>
@@ -1017,21 +977,11 @@
       <c r="L6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
         <v>81</v>
       </c>
@@ -1073,21 +1023,11 @@
       <c r="L7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
       <c r="R7" s="5" t="s">
         <v>81</v>
       </c>
@@ -1129,21 +1069,11 @@
       <c r="L8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
       <c r="R8" s="5" t="s">
         <v>81</v>
       </c>
@@ -1185,21 +1115,11 @@
       <c r="L9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
       <c r="R9" s="5" t="s">
         <v>81</v>
       </c>
@@ -1241,21 +1161,11 @@
       <c r="L10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
       <c r="R10" s="5" t="s">
         <v>81</v>
       </c>
@@ -1297,21 +1207,11 @@
       <c r="L11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
       <c r="R11" s="5" t="s">
         <v>81</v>
       </c>
@@ -1353,21 +1253,11 @@
       <c r="L12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
       <c r="R12" s="5" t="s">
         <v>81</v>
       </c>
@@ -1409,21 +1299,11 @@
       <c r="L13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
       <c r="R13" s="5" t="s">
         <v>81</v>
       </c>
@@ -1465,21 +1345,11 @@
       <c r="L14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
       <c r="R14" s="5" t="s">
         <v>81</v>
       </c>
@@ -1799,21 +1669,11 @@
       <c r="L20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
       <c r="R20" s="5" t="s">
         <v>81</v>
       </c>
@@ -1901,21 +1761,11 @@
       <c r="L22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
       <c r="R22" s="5" t="s">
         <v>81</v>
       </c>
